--- a/output/yearly_surface_area_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_34_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635136834</v>
+        <v>10.84497641841</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907200864867</v>
+        <v>37.78907224225382</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.300054944601029</v>
+        <v>4.715334223497431</v>
       </c>
       <c r="C2" t="n">
-        <v>7.431830121148354</v>
+        <v>10.77271755870025</v>
       </c>
       <c r="D2" t="n">
-        <v>21.17924322371644</v>
+        <v>20.96718571959913</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.65611056607313</v>
+        <v>17.02841393016093</v>
       </c>
       <c r="C3" t="n">
-        <v>46.15686831516379</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D3" t="n">
-        <v>75.32459260833653</v>
+        <v>72.64933011426398</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.61776565234527</v>
+        <v>34.79117514309847</v>
       </c>
       <c r="C4" t="n">
-        <v>95.6948757237536</v>
+        <v>99.79170889357553</v>
       </c>
       <c r="D4" t="n">
-        <v>105.5987465641954</v>
+        <v>99.90657337497241</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.67456815047135</v>
+        <v>42.28878236043136</v>
       </c>
       <c r="C5" t="n">
-        <v>152.4163310843173</v>
+        <v>137.4692222871597</v>
       </c>
       <c r="D5" t="n">
-        <v>81.6323216081223</v>
+        <v>73.65562151111696</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.5359207399943</v>
+        <v>39.7686360036298</v>
       </c>
       <c r="C6" t="n">
-        <v>157.6254844030509</v>
+        <v>144.7852061792069</v>
       </c>
       <c r="D6" t="n">
-        <v>52.00513938936205</v>
+        <v>48.66425195181016</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.91282974296706</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="C7" t="n">
-        <v>143.7877505116921</v>
+        <v>133.7866866485298</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>14.43659999094934</v>
       </c>
       <c r="C8" t="n">
-        <v>93.46238144429634</v>
+        <v>90.79202768874502</v>
       </c>
       <c r="D8" t="n">
-        <v>35.38218726105504</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>47.48124596819272</v>
+        <v>48.14687091167205</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
         <v>34.59188035913637</v>
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -965,7 +965,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -982,7 +982,7 @@
         <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.63642893403407</v>
+        <v>7.648854101188797</v>
       </c>
       <c r="C21" t="n">
-        <v>92.5917008251631</v>
+        <v>92.74235597691415</v>
       </c>
       <c r="D21" t="n">
-        <v>7.63642893403407</v>
+        <v>7.648854101188797</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.318528224532471</v>
+        <v>5.621487354517236</v>
       </c>
       <c r="C2" t="n">
-        <v>6.71908128786517</v>
+        <v>11.94786956068368</v>
       </c>
       <c r="D2" t="n">
-        <v>21.70447824548848</v>
+        <v>17.44565670446582</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.80337272171015</v>
+        <v>16.2037458585936</v>
       </c>
       <c r="C3" t="n">
-        <v>37.45367491701582</v>
+        <v>38.21452938780709</v>
       </c>
       <c r="D3" t="n">
-        <v>74.29375751887737</v>
+        <v>72.00137662946108</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.9631198600619</v>
+        <v>33.08097064230052</v>
       </c>
       <c r="C4" t="n">
-        <v>104.6670679928652</v>
+        <v>93.14233169271189</v>
       </c>
       <c r="D4" t="n">
-        <v>116.2428551736393</v>
+        <v>109.5679525324653</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.33157834879072</v>
+        <v>46.26486056263094</v>
       </c>
       <c r="C5" t="n">
-        <v>161.4238662707818</v>
+        <v>158.6258853136784</v>
       </c>
       <c r="D5" t="n">
-        <v>95.84311962709488</v>
+        <v>89.60902170512763</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.25794727097221</v>
+        <v>47.21519234034186</v>
       </c>
       <c r="C6" t="n">
-        <v>195.14002767773</v>
+        <v>176.1009944492716</v>
       </c>
       <c r="D6" t="n">
-        <v>63.07434475474484</v>
+        <v>57.92213280285758</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.79978988825843</v>
+        <v>36.47094546506476</v>
       </c>
       <c r="C7" t="n">
-        <v>179.6598298771663</v>
+        <v>166.7842087359694</v>
       </c>
       <c r="D7" t="n">
-        <v>44.6155244194963</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.10971906316416</v>
+        <v>20.9455872701057</v>
       </c>
       <c r="C8" t="n">
-        <v>135.4370045393687</v>
+        <v>130.0962970282661</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>10.42812411450962</v>
       </c>
       <c r="C9" t="n">
-        <v>77.54530591534278</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D9" t="n">
-        <v>34.72343455150543</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1321,7 +1321,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.802187227796705</v>
+        <v>7.817616874426817</v>
       </c>
       <c r="C21" t="n">
-        <v>100.4531605578826</v>
+        <v>100.6518172582453</v>
       </c>
       <c r="D21" t="n">
-        <v>8.777460631271293</v>
+        <v>8.794818983730169</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.116288197457628</v>
+        <v>7.224681355552278</v>
       </c>
       <c r="C2" t="n">
-        <v>8.355654710844604</v>
+        <v>10.8178779530956</v>
       </c>
       <c r="D2" t="n">
-        <v>23.22520543936679</v>
+        <v>16.71916340332318</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.48845269282518</v>
+        <v>16.93023915973625</v>
       </c>
       <c r="C3" t="n">
-        <v>32.13751109851934</v>
+        <v>41.4592055503428</v>
       </c>
       <c r="D3" t="n">
-        <v>73.48872440139499</v>
+        <v>69.21812188792136</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.41883072128167</v>
+        <v>31.23037621979529</v>
       </c>
       <c r="C4" t="n">
-        <v>98.54096231836509</v>
+        <v>92.87431456945251</v>
       </c>
       <c r="D4" t="n">
-        <v>121.9222656427071</v>
+        <v>117.4042627077633</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.15977250054753</v>
+        <v>47.59021996336414</v>
       </c>
       <c r="C5" t="n">
-        <v>172.1985473248906</v>
+        <v>163.5837112201248</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0784613386736</v>
+        <v>102.2981107825177</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.57116584635595</v>
+        <v>52.76992085097032</v>
       </c>
       <c r="C6" t="n">
-        <v>220.2168092873063</v>
+        <v>205.1626899903857</v>
       </c>
       <c r="D6" t="n">
-        <v>73.37876865851936</v>
+        <v>69.11209313586272</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.38731698375453</v>
+        <v>44.01665831990574</v>
       </c>
       <c r="C7" t="n">
-        <v>219.0053326202657</v>
+        <v>201.4585559022625</v>
       </c>
       <c r="D7" t="n">
-        <v>49.94543270585223</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.20146356801562</v>
+        <v>28.03871443328891</v>
       </c>
       <c r="C8" t="n">
-        <v>175.6592079823605</v>
+        <v>168.0653894900115</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.31249886958674</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>112.8234279197477</v>
+        <v>109.3843657117711</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>61.21196935978863</v>
+        <v>61.35432277690443</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.02701557629594</v>
+        <v>39.09319358310798</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.951499466411183</v>
+        <v>7.970121435402933</v>
       </c>
       <c r="C21" t="n">
-        <v>107.345242796551</v>
+        <v>107.5966393779396</v>
       </c>
       <c r="D21" t="n">
-        <v>9.939374333013978</v>
+        <v>9.962651794253667</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.685300955293279</v>
+        <v>6.593417581721578</v>
       </c>
       <c r="C2" t="n">
-        <v>5.88165049614264</v>
+        <v>7.615416941842508</v>
       </c>
       <c r="D2" t="n">
-        <v>19.42584182393164</v>
+        <v>14.03899217072939</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.77101610519901</v>
+        <v>20.61670178918302</v>
       </c>
       <c r="C3" t="n">
-        <v>51.59575059669112</v>
+        <v>60.42166245786995</v>
       </c>
       <c r="D3" t="n">
-        <v>81.17090018712628</v>
+        <v>76.99847244407734</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.76945352041802</v>
+        <v>22.85803179797848</v>
       </c>
       <c r="C4" t="n">
-        <v>137.033326306474</v>
+        <v>130.6902543893354</v>
       </c>
       <c r="D4" t="n">
-        <v>118.5273820814217</v>
+        <v>113.9200401053914</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.23720739599601</v>
+        <v>29.72241174607219</v>
       </c>
       <c r="C5" t="n">
-        <v>131.5787360616788</v>
+        <v>122.5957445678205</v>
       </c>
       <c r="D5" t="n">
-        <v>72.3793494955961</v>
+        <v>67.81422267084844</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.82898027747859</v>
+        <v>27.33087433852696</v>
       </c>
       <c r="C6" t="n">
-        <v>144.2216829969692</v>
+        <v>132.669457761097</v>
       </c>
       <c r="D6" t="n">
-        <v>32.88560284915541</v>
+        <v>31.67805317293184</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="C7" t="n">
-        <v>123.4861897355723</v>
+        <v>118.1562814492164</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>28.20659329071511</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>83.11476064153496</v>
+        <v>80.6113039957056</v>
       </c>
       <c r="D8" t="n">
-        <v>26.36974333606933</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>46.70468353413349</v>
+        <v>46.81562102471339</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>27.8983245115816</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.25291535926396</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.430226478638355</v>
+        <v>4.028110830524663</v>
       </c>
       <c r="C2" t="n">
-        <v>2.716495897650924</v>
+        <v>3.889684404225862</v>
       </c>
       <c r="D2" t="n">
-        <v>14.14109393197106</v>
+        <v>10.24650078922396</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.51223562190536</v>
+        <v>22.05005343738336</v>
       </c>
       <c r="C3" t="n">
-        <v>38.2734342500619</v>
+        <v>45.9703362513569</v>
       </c>
       <c r="D3" t="n">
-        <v>78.66744354129692</v>
+        <v>71.81484456565418</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.26567807941916</v>
+        <v>29.86476516318797</v>
       </c>
       <c r="C4" t="n">
-        <v>136.8546482243011</v>
+        <v>144.8951619220825</v>
       </c>
       <c r="D4" t="n">
-        <v>130.5115763071625</v>
+        <v>125.0618948008884</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.76520773443155</v>
+        <v>33.13398501832986</v>
       </c>
       <c r="C5" t="n">
-        <v>187.0720250442297</v>
+        <v>176.591868301395</v>
       </c>
       <c r="D5" t="n">
-        <v>89.48630324209678</v>
+        <v>84.47938995043805</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.13590745600934</v>
+        <v>32.12082138754715</v>
       </c>
       <c r="C6" t="n">
-        <v>176.4230076962646</v>
+        <v>161.8116566139593</v>
       </c>
       <c r="D6" t="n">
-        <v>40.85543071223103</v>
+        <v>39.08435785376978</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>17.24734366820796</v>
       </c>
       <c r="C7" t="n">
-        <v>155.4057528437488</v>
+        <v>148.6984525283346</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>108.9838126484384</v>
+        <v>104.6444877956675</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>49.47812079863073</v>
+        <v>50.80937068558941</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
         <v>29.18245050873644</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.740057842552848</v>
+        <v>3.292781800043802</v>
       </c>
       <c r="C2" t="n">
-        <v>8.435176274888596</v>
+        <v>14.30013706005904</v>
       </c>
       <c r="D2" t="n">
-        <v>12.18348900970292</v>
+        <v>12.29933523880404</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.76195939168254</v>
+        <v>17.87762569433442</v>
       </c>
       <c r="C3" t="n">
-        <v>24.06263623108932</v>
+        <v>30.28200793749286</v>
       </c>
       <c r="D3" t="n">
-        <v>73.05184667300516</v>
+        <v>64.18666490365646</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.9495963763807</v>
+        <v>35.55693835241098</v>
       </c>
       <c r="C4" t="n">
-        <v>116.4342959759675</v>
+        <v>129.9372539001781</v>
       </c>
       <c r="D4" t="n">
-        <v>136.6504447018178</v>
+        <v>131.3156276769406</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>38.28816046562561</v>
       </c>
       <c r="C5" t="n">
-        <v>219.2978934361313</v>
+        <v>218.9542817396449</v>
       </c>
       <c r="D5" t="n">
-        <v>111.5510828950438</v>
+        <v>105.8569462104124</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.72459622565894</v>
+        <v>37.51454327467913</v>
       </c>
       <c r="C6" t="n">
-        <v>229.8369550412208</v>
+        <v>217.077180129125</v>
       </c>
       <c r="D6" t="n">
-        <v>55.54728510628455</v>
+        <v>52.89067581859268</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.39759212468673</v>
+        <v>25.27214940272139</v>
       </c>
       <c r="C7" t="n">
-        <v>200.919576412631</v>
+        <v>187.9241820515159</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>151.0418842983718</v>
+        <v>143.7818600254666</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>83.53593040665682</v>
+        <v>83.75780538781659</v>
       </c>
       <c r="D9" t="n">
         <v>28.95468504135117</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>42.56367171762047</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
         <v>16.84188186635403</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.66209886328985</v>
+        <v>2.00374706436774</v>
       </c>
       <c r="C2" t="n">
-        <v>4.073271224920016</v>
+        <v>6.932120539686728</v>
       </c>
       <c r="D2" t="n">
-        <v>8.496044632551897</v>
+        <v>8.610909113948773</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.7753029489145</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="C3" t="n">
-        <v>29.20208546282137</v>
+        <v>42.64712027248144</v>
       </c>
       <c r="D3" t="n">
-        <v>70.15078220695584</v>
+        <v>62.46860642122455</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.089225534562</v>
+        <v>39.09221183540375</v>
       </c>
       <c r="C4" t="n">
-        <v>109.7466306146382</v>
+        <v>123.9770635876957</v>
       </c>
       <c r="D4" t="n">
-        <v>146.0820948965169</v>
+        <v>137.7480386351657</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.80295611554943</v>
+        <v>39.83441309981433</v>
       </c>
       <c r="C5" t="n">
-        <v>256.015257574962</v>
+        <v>262.2248118043231</v>
       </c>
       <c r="D5" t="n">
-        <v>113.9563647704485</v>
+        <v>110.6429662686156</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.60634453279281</v>
+        <v>30.22899356146354</v>
       </c>
       <c r="C6" t="n">
-        <v>263.8898559107257</v>
+        <v>248.1112068080709</v>
       </c>
       <c r="D6" t="n">
-        <v>53.61520562432682</v>
+        <v>51.20010627187966</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>203.3749274209522</v>
+        <v>193.313976947831</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>104.4775906859456</v>
+        <v>102.558273924143</v>
       </c>
       <c r="D8" t="n">
         <v>31.04286240828414</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
         <v>23.06125357275758</v>
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>18.8358114536793</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.31977201414398</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.472040719293469</v>
+        <v>2.86866679180918</v>
       </c>
       <c r="C2" t="n">
-        <v>8.183848862601412</v>
+        <v>9.154797342101507</v>
       </c>
       <c r="D2" t="n">
-        <v>7.853981633974483</v>
+        <v>12.86285842104171</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.51942665100457</v>
+        <v>12.22766765639402</v>
       </c>
       <c r="C3" t="n">
-        <v>22.67837196810132</v>
+        <v>35.00421439492003</v>
       </c>
       <c r="D3" t="n">
-        <v>62.00227626170732</v>
+        <v>55.88107932572845</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.26866438026091</v>
+        <v>35.87600635629119</v>
       </c>
       <c r="C4" t="n">
-        <v>92.19789040122646</v>
+        <v>116.6767876589164</v>
       </c>
       <c r="D4" t="n">
-        <v>147.2179769903304</v>
+        <v>137.339631590199</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.47884050442774</v>
+        <v>47.5411325781518</v>
       </c>
       <c r="C5" t="n">
-        <v>233.7050409959533</v>
+        <v>246.7131980772235</v>
       </c>
       <c r="D5" t="n">
-        <v>134.5239791744192</v>
+        <v>130.5479009722196</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>39.04410619789565</v>
       </c>
       <c r="C6" t="n">
-        <v>327.0044523213446</v>
+        <v>324.1465847542822</v>
       </c>
       <c r="D6" t="n">
-        <v>71.32593420893927</v>
+        <v>66.77749709516381</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.43267300013236</v>
+        <v>16.22927129890402</v>
       </c>
       <c r="C7" t="n">
-        <v>279.5506952888708</v>
+        <v>260.5666399318502</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>167.8150438254285</v>
+        <v>161.7232993205771</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>32.7952820603647</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67499442329461</v>
+        <v>65.23124446097505</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
         <v>24.34243432679967</v>
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>21.85664913964673</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.758310138306037</v>
+        <v>1.938951715887451</v>
       </c>
       <c r="C2" t="n">
-        <v>5.004949796250239</v>
+        <v>4.873395603881167</v>
       </c>
       <c r="D2" t="n">
-        <v>6.962554718518379</v>
+        <v>9.220574438286043</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.714393533522189</v>
+        <v>11.28518986031709</v>
       </c>
       <c r="C3" t="n">
-        <v>26.81152980298039</v>
+        <v>35.87796985169969</v>
       </c>
       <c r="D3" t="n">
-        <v>56.18051237552373</v>
+        <v>53.87340527054372</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.56747553525043</v>
+        <v>32.03442758957343</v>
       </c>
       <c r="C4" t="n">
-        <v>80.1626452948648</v>
+        <v>106.8750185797163</v>
       </c>
       <c r="D4" t="n">
-        <v>145.8906540941888</v>
+        <v>135.4635117273834</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.86587008407924</v>
+        <v>50.82998738737862</v>
       </c>
       <c r="C5" t="n">
-        <v>216.6226309420587</v>
+        <v>243.5470617310275</v>
       </c>
       <c r="D5" t="n">
-        <v>148.6856898081795</v>
+        <v>143.1879026643973</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.44662275663685</v>
+        <v>45.00135126726531</v>
       </c>
       <c r="C6" t="n">
-        <v>357.1126909151858</v>
+        <v>360.4133266968636</v>
       </c>
       <c r="D6" t="n">
-        <v>83.32092765942681</v>
+        <v>78.61148392215486</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.87562114119692</v>
+        <v>14.43267300013236</v>
       </c>
       <c r="C7" t="n">
-        <v>345.2463064139546</v>
+        <v>326.0825912270568</v>
       </c>
       <c r="D7" t="n">
-        <v>44.19631814978291</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>216.2986541996572</v>
+        <v>204.8662021837031</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.442187377538564</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>71.88749389576842</v>
+        <v>69.33593161243097</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.938951715887451</v>
+        <v>3.4626241528785</v>
       </c>
       <c r="C2" t="n">
-        <v>7.276713983877358</v>
+        <v>7.71948219849267</v>
       </c>
       <c r="D2" t="n">
-        <v>17.73429052951438</v>
+        <v>17.3278469799562</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.92270397327176</v>
+        <v>9.076257525761761</v>
       </c>
       <c r="C3" t="n">
-        <v>23.33614292994668</v>
+        <v>28.50504459280614</v>
       </c>
       <c r="D3" t="n">
-        <v>50.28020867300039</v>
+        <v>49.63716392671873</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.27920156310037</v>
+        <v>27.0697294491973</v>
       </c>
       <c r="C4" t="n">
-        <v>74.27903130331367</v>
+        <v>99.29396280752239</v>
       </c>
       <c r="D4" t="n">
-        <v>141.4747529204866</v>
+        <v>131.953763684701</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.88412237983243</v>
+        <v>49.60280275707011</v>
       </c>
       <c r="C5" t="n">
-        <v>188.1274038262951</v>
+        <v>224.2311756499715</v>
       </c>
       <c r="D5" t="n">
-        <v>159.1903902436203</v>
+        <v>153.4717098663827</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.65166915810419</v>
+        <v>53.09193409796327</v>
       </c>
       <c r="C6" t="n">
-        <v>353.5705451982633</v>
+        <v>371.4422804063723</v>
       </c>
       <c r="D6" t="n">
-        <v>102.279457576137</v>
+        <v>94.83290123942491</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.2360046641135</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>410.7023710992021</v>
+        <v>398.0064097878824</v>
       </c>
       <c r="D7" t="n">
-        <v>53.11942303368217</v>
+        <v>51.56237117474672</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>306.5065420043754</v>
+        <v>285.3940576245478</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>138.0062382813826</v>
+        <v>131.571863827749</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>47.26133448244146</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3753,7 +3753,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.091744504851459</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.622469102221483</v>
+        <v>5.527239574909543</v>
       </c>
       <c r="C2" t="n">
-        <v>9.457175635009525</v>
+        <v>11.66021748333937</v>
       </c>
       <c r="D2" t="n">
-        <v>20.30450601923253</v>
+        <v>5.431028299893355</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.4156801895239</v>
+        <v>2.554507526450201</v>
       </c>
       <c r="C2" t="n">
-        <v>4.306927178530757</v>
+        <v>4.630903920932204</v>
       </c>
       <c r="D2" t="n">
-        <v>13.19370739737288</v>
+        <v>12.89231085216911</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.4948829583984</v>
+        <v>12.38474728907351</v>
       </c>
       <c r="C3" t="n">
-        <v>28.45104846907257</v>
+        <v>33.89974822764236</v>
       </c>
       <c r="D3" t="n">
-        <v>57.41260574435347</v>
+        <v>56.39649687045802</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.77466535857552</v>
+        <v>37.66278717802039</v>
       </c>
       <c r="C4" t="n">
-        <v>108.1130024347715</v>
+        <v>137.5693605529928</v>
       </c>
       <c r="D4" t="n">
-        <v>144.805822880996</v>
+        <v>136.4590038994896</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.67899386290708</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="C5" t="n">
-        <v>290.6218641496621</v>
+        <v>324.1240045570845</v>
       </c>
       <c r="D5" t="n">
-        <v>145.7649903880452</v>
+        <v>137.9110087540707</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.41009280293469</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="C6" t="n">
-        <v>332.8811940789661</v>
+        <v>324.0258297866598</v>
       </c>
       <c r="D6" t="n">
-        <v>79.89953691012668</v>
+        <v>75.39135145222532</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.311835917051991</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>215.5319092426405</v>
+        <v>200.6800299727947</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.335176877775662</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>101.7237883755332</v>
+        <v>96.96722074845746</v>
       </c>
       <c r="D8" t="n">
-        <v>23.86628669023996</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.27655941962388</v>
+        <v>36.0546844384641</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>19.92947839621025</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D10" t="n">
-        <v>18.50594422505238</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>14.9264920953685</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4361,7 +4361,7 @@
         <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>4.916592502868027</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.849252821902496</v>
+        <v>7.395505456091222</v>
       </c>
       <c r="C2" t="n">
-        <v>11.34998520879738</v>
+        <v>4.841979677345269</v>
       </c>
       <c r="D2" t="n">
-        <v>18.75138115111408</v>
+        <v>24.39839394594173</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.94296082216245</v>
+        <v>11.74170254279185</v>
       </c>
       <c r="C3" t="n">
-        <v>23.83192552059132</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D3" t="n">
-        <v>20.18964153783566</v>
+        <v>7.696902001294993</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39593292823339</v>
+        <v>13.39811892905498</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13164885957482</v>
+        <v>70.14309321681725</v>
       </c>
       <c r="D21" t="n">
-        <v>1.575992109203929</v>
+        <v>1.576249285771174</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.249004063980196</v>
+        <v>4.643666641087413</v>
       </c>
       <c r="C2" t="n">
-        <v>6.525676990128549</v>
+        <v>9.099819470663686</v>
       </c>
       <c r="D2" t="n">
-        <v>23.37835808122929</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.91551294417254</v>
+        <v>19.98838325846506</v>
       </c>
       <c r="C3" t="n">
-        <v>36.6142806298848</v>
+        <v>22.81090790817464</v>
       </c>
       <c r="D3" t="n">
-        <v>31.06249736236908</v>
+        <v>26.33047342789946</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.92412768933251</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="C4" t="n">
-        <v>36.87149852839745</v>
+        <v>45.32041927114551</v>
       </c>
       <c r="D4" t="n">
-        <v>25.65306751196916</v>
+        <v>19.10579207234717</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4896,10 +4896,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43455841261589</v>
+        <v>15.43809274759965</v>
       </c>
       <c r="C21" t="n">
-        <v>86.10858903880445</v>
+        <v>86.12830690766121</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249380718445451</v>
+        <v>3.250124788968348</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.843542262126263</v>
+        <v>4.171445995344697</v>
       </c>
       <c r="C2" t="n">
-        <v>6.417684742661399</v>
+        <v>6.71613604475243</v>
       </c>
       <c r="D2" t="n">
-        <v>33.38923942143402</v>
+        <v>28.09467405243097</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.64905840569416</v>
+        <v>17.95616551067416</v>
       </c>
       <c r="C3" t="n">
-        <v>29.89912633283661</v>
+        <v>30.30655163009904</v>
       </c>
       <c r="D3" t="n">
-        <v>42.553854240578</v>
+        <v>42.68639018065132</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.26193101505142</v>
+        <v>27.42708561354314</v>
       </c>
       <c r="C4" t="n">
-        <v>68.57409539393547</v>
+        <v>52.16123727433728</v>
       </c>
       <c r="D4" t="n">
-        <v>35.4420738710141</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.27184630308513</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="C5" t="n">
-        <v>40.49709280018094</v>
+        <v>49.21010367537139</v>
       </c>
       <c r="D5" t="n">
-        <v>32.12769362147687</v>
+        <v>29.550605897829</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.39663573917827</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72015323414298</v>
+        <v>16.72490529259195</v>
       </c>
       <c r="C21" t="n">
-        <v>101.156927066565</v>
+        <v>102.0219222848109</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180038308535744</v>
+        <v>4.181226323147988</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.03243873196915</v>
+        <v>5.739297079026853</v>
       </c>
       <c r="C2" t="n">
-        <v>11.8349685746953</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="D2" t="n">
-        <v>26.4070497488307</v>
+        <v>22.68818944514379</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.26970288122739</v>
+        <v>15.93376523992573</v>
       </c>
       <c r="C3" t="n">
-        <v>27.03242303643592</v>
+        <v>27.86690858504571</v>
       </c>
       <c r="D3" t="n">
-        <v>58.46307578789757</v>
+        <v>54.54099370943155</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.5164246546296</v>
+        <v>31.37076614150258</v>
       </c>
       <c r="C4" t="n">
-        <v>71.98174167537614</v>
+        <v>65.12816095202915</v>
       </c>
       <c r="D4" t="n">
-        <v>48.07716682467056</v>
+        <v>42.27012915405066</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.93010029101601</v>
+        <v>26.11448893296516</v>
       </c>
       <c r="C5" t="n">
-        <v>86.12381735505146</v>
+        <v>73.70470889632931</v>
       </c>
       <c r="D5" t="n">
-        <v>37.35550014659114</v>
+        <v>32.54493639578177</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.18996033300515</v>
+        <v>11.02895370950867</v>
       </c>
       <c r="C6" t="n">
-        <v>38.56108632740622</v>
+        <v>46.249152599363</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>37.91705983342032</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.43940636534185</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
         <v>39.55461500410399</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03214180420702</v>
+        <v>18.03992220099619</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7795850177217</v>
+        <v>117.6890162636418</v>
       </c>
       <c r="D21" t="n">
-        <v>6.010713934735674</v>
+        <v>6.013307400332063</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.937610115284709</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C2" t="n">
-        <v>14.28442909679109</v>
+        <v>14.07629858349077</v>
       </c>
       <c r="D2" t="n">
-        <v>31.22252223816131</v>
+        <v>29.13925360974958</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.09298829446296</v>
+        <v>15.93867397844697</v>
       </c>
       <c r="C3" t="n">
-        <v>35.12202411942965</v>
+        <v>28.06325812589508</v>
       </c>
       <c r="D3" t="n">
-        <v>61.12361206640642</v>
+        <v>56.12651625179015</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.98641976305657</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="C4" t="n">
-        <v>57.52157973952487</v>
+        <v>56.5133248472634</v>
       </c>
       <c r="D4" t="n">
-        <v>55.86242611934776</v>
+        <v>51.62520302781852</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.70858516275472</v>
+        <v>22.43293504203962</v>
       </c>
       <c r="C5" t="n">
-        <v>82.19682653806422</v>
+        <v>72.40389318820228</v>
       </c>
       <c r="D5" t="n">
-        <v>37.03643214271093</v>
+        <v>32.37313054753858</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.7132318593687</v>
+        <v>12.43776166510284</v>
       </c>
       <c r="C6" t="n">
-        <v>59.12968247908115</v>
+        <v>55.99005332089985</v>
       </c>
       <c r="D6" t="n">
-        <v>31.43654323768712</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>24.67328330313084</v>
+        <v>27.96704685087888</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.04137131452171</v>
+        <v>7.045960765671207</v>
       </c>
       <c r="C21" t="n">
-        <v>66.01285607364103</v>
+        <v>66.05588217816756</v>
       </c>
       <c r="D21" t="n">
-        <v>4.400857071576069</v>
+        <v>4.403725478544505</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.285328729037327</v>
+        <v>5.46637121724624</v>
       </c>
       <c r="C2" t="n">
-        <v>7.684139281139785</v>
+        <v>10.57145927932965</v>
       </c>
       <c r="D2" t="n">
-        <v>24.19419042345839</v>
+        <v>24.55252833550848</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.99543541884404</v>
+        <v>19.63986282345744</v>
       </c>
       <c r="C3" t="n">
-        <v>48.00255399914779</v>
+        <v>45.14566817978957</v>
       </c>
       <c r="D3" t="n">
-        <v>72.58060777496669</v>
+        <v>67.03864198449345</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.59376173908685</v>
+        <v>27.5164246546296</v>
       </c>
       <c r="C4" t="n">
-        <v>76.10410028550849</v>
+        <v>65.12816095202915</v>
       </c>
       <c r="D4" t="n">
-        <v>74.9299300312293</v>
+        <v>69.05907875983338</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.50089661781091</v>
+        <v>29.08427573831176</v>
       </c>
       <c r="C5" t="n">
-        <v>95.79403224188253</v>
+        <v>91.76886665447061</v>
       </c>
       <c r="D5" t="n">
-        <v>49.40645321622075</v>
+        <v>43.9086660724386</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.16607959293373</v>
+        <v>22.37992066601029</v>
       </c>
       <c r="C6" t="n">
-        <v>100.5486363735499</v>
+        <v>90.24421246977532</v>
       </c>
       <c r="D6" t="n">
-        <v>36.02523200733671</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>10.77958979262998</v>
       </c>
       <c r="C7" t="n">
-        <v>59.34763046942393</v>
+        <v>58.26967149016093</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>26.78698611037422</v>
+        <v>29.12354564648163</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.255095239622975</v>
+        <v>7.262059478878444</v>
       </c>
       <c r="C21" t="n">
-        <v>75.27161311108837</v>
+        <v>75.34386709336387</v>
       </c>
       <c r="D21" t="n">
-        <v>5.441321429717231</v>
+        <v>5.446544609158833</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.374266859496287</v>
+        <v>4.435536127787089</v>
       </c>
       <c r="C2" t="n">
-        <v>13.98303255158732</v>
+        <v>7.505461198966865</v>
       </c>
       <c r="D2" t="n">
-        <v>23.10248697633594</v>
+        <v>23.50893052589412</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.17920216598743</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="C3" t="n">
-        <v>37.48803608666446</v>
+        <v>42.73547756586365</v>
       </c>
       <c r="D3" t="n">
-        <v>74.82390127917066</v>
+        <v>70.78891821471626</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.26040948799944</v>
+        <v>33.10649608261094</v>
       </c>
       <c r="C4" t="n">
-        <v>99.97038697574845</v>
+        <v>92.36380576324416</v>
       </c>
       <c r="D4" t="n">
-        <v>92.68287376712438</v>
+        <v>85.48469959958678</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.31775176547326</v>
+        <v>35.78470381979624</v>
       </c>
       <c r="C5" t="n">
-        <v>120.4849870036898</v>
+        <v>106.6423443738098</v>
       </c>
       <c r="D5" t="n">
-        <v>65.16350386938205</v>
+        <v>58.78214379177778</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.6126359296458</v>
+        <v>31.15478164656829</v>
       </c>
       <c r="C6" t="n">
-        <v>128.2015239590697</v>
+        <v>120.4329543753648</v>
       </c>
       <c r="D6" t="n">
-        <v>43.27053006467818</v>
+        <v>40.01014593887452</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>103.8433816690021</v>
+        <v>96.95642152371074</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>54.15811210477529</v>
+        <v>54.57535487908019</v>
       </c>
       <c r="D8" t="n">
         <v>33.54631905411351</v>
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.95468504135117</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
         <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6552,7 +6552,7 @@
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.454074613336165</v>
+        <v>7.463471043871384</v>
       </c>
       <c r="C21" t="n">
-        <v>83.85833940003187</v>
+        <v>83.96404924355308</v>
       </c>
       <c r="D21" t="n">
-        <v>6.522315286669145</v>
+        <v>6.530537163387462</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_34_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641841</v>
+        <v>10.84497634344255</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907224225382</v>
+        <v>37.78907198103142</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.715334223497431</v>
+        <v>5.750096303773569</v>
       </c>
       <c r="C2" t="n">
-        <v>10.77271755870025</v>
+        <v>9.503317777109125</v>
       </c>
       <c r="D2" t="n">
-        <v>20.96718571959913</v>
+        <v>29.11176467403067</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.02841393016093</v>
+        <v>15.90922154731956</v>
       </c>
       <c r="C3" t="n">
-        <v>35.3036474447153</v>
+        <v>23.68957210347553</v>
       </c>
       <c r="D3" t="n">
-        <v>72.64933011426398</v>
+        <v>56.98554549300611</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.79117514309847</v>
+        <v>35.90153179660161</v>
       </c>
       <c r="C4" t="n">
-        <v>99.79170889357553</v>
+        <v>77.26550781963248</v>
       </c>
       <c r="D4" t="n">
-        <v>99.90657337497241</v>
+        <v>81.00498482510856</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.28878236043136</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="C5" t="n">
-        <v>137.4692222871597</v>
+        <v>137.5673970575843</v>
       </c>
       <c r="D5" t="n">
-        <v>73.65562151111696</v>
+        <v>61.87464906015524</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.7686360036298</v>
+        <v>39.1246095096439</v>
       </c>
       <c r="C6" t="n">
-        <v>144.7852061792069</v>
+        <v>151.6682393336813</v>
       </c>
       <c r="D6" t="n">
-        <v>48.66425195181016</v>
+        <v>44.23656980565704</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.5478405811655</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>133.7866866485298</v>
+        <v>122.5280039762274</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.43659999094934</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>90.79202768874502</v>
+        <v>74.43611093599316</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>48.14687091167205</v>
+        <v>40.82499653339935</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.648854101188797</v>
+        <v>7.683800288756356</v>
       </c>
       <c r="C21" t="n">
-        <v>92.74235597691415</v>
+        <v>93.16607850117082</v>
       </c>
       <c r="D21" t="n">
-        <v>7.648854101188797</v>
+        <v>8.6442753248509</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.621487354517236</v>
+        <v>6.575746123045136</v>
       </c>
       <c r="C2" t="n">
-        <v>11.94786956068368</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="D2" t="n">
-        <v>17.44565670446582</v>
+        <v>22.58706943160637</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.2037458585936</v>
+        <v>17.42602175038088</v>
       </c>
       <c r="C3" t="n">
-        <v>38.21452938780709</v>
+        <v>30.22310307523806</v>
       </c>
       <c r="D3" t="n">
-        <v>72.00137662946108</v>
+        <v>65.19786503903067</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.08097064230052</v>
+        <v>32.80019079888594</v>
       </c>
       <c r="C4" t="n">
-        <v>93.14233169271189</v>
+        <v>67.54031506136356</v>
       </c>
       <c r="D4" t="n">
-        <v>109.5679525324653</v>
+        <v>89.49219372832225</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.26486056263094</v>
+        <v>48.79286090106649</v>
       </c>
       <c r="C5" t="n">
-        <v>158.6258853136784</v>
+        <v>139.7763293921396</v>
       </c>
       <c r="D5" t="n">
-        <v>89.60902170512763</v>
+        <v>73.80288366675398</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.21519234034186</v>
+        <v>48.18123208132072</v>
       </c>
       <c r="C6" t="n">
-        <v>176.1009944492716</v>
+        <v>181.3739613687813</v>
       </c>
       <c r="D6" t="n">
-        <v>57.92213280285758</v>
+        <v>52.40765594810324</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.47094546506476</v>
+        <v>35.45287309576081</v>
       </c>
       <c r="C7" t="n">
-        <v>166.7842087359694</v>
+        <v>167.9220543251914</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>41.9206269713388</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.9455872701057</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="C8" t="n">
-        <v>130.0962970282661</v>
+        <v>114.2410716046801</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>75.99218104722434</v>
+        <v>64.6765570080756</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
         <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.817616874426817</v>
+        <v>7.860897053161644</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6518172582453</v>
+        <v>101.2090495594562</v>
       </c>
       <c r="D21" t="n">
-        <v>8.794818983730169</v>
+        <v>9.826121316452054</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.224681355552278</v>
+        <v>7.448519832120549</v>
       </c>
       <c r="C2" t="n">
-        <v>10.8178779530956</v>
+        <v>12.83438773761855</v>
       </c>
       <c r="D2" t="n">
-        <v>16.71916340332318</v>
+        <v>28.76618948213579</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.93023915973625</v>
+        <v>19.08517537055799</v>
       </c>
       <c r="C3" t="n">
-        <v>41.4592055503428</v>
+        <v>31.80371687907542</v>
       </c>
       <c r="D3" t="n">
-        <v>69.21812188792136</v>
+        <v>66.74902641174064</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.23037621979529</v>
+        <v>32.16205479112551</v>
       </c>
       <c r="C4" t="n">
-        <v>92.87431456945251</v>
+        <v>70.89691046218341</v>
       </c>
       <c r="D4" t="n">
-        <v>117.4042627077633</v>
+        <v>97.43060566486196</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.59021996336414</v>
+        <v>48.64559874542947</v>
       </c>
       <c r="C5" t="n">
-        <v>163.5837112201248</v>
+        <v>131.4314739060418</v>
       </c>
       <c r="D5" t="n">
-        <v>102.2981107825177</v>
+        <v>85.70657458074656</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.76992085097032</v>
+        <v>55.2252718592916</v>
       </c>
       <c r="C6" t="n">
-        <v>205.1626899903857</v>
+        <v>197.2733654390584</v>
       </c>
       <c r="D6" t="n">
-        <v>69.11209313586272</v>
+        <v>60.41773546705297</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.01665831990574</v>
+        <v>44.43586458961913</v>
       </c>
       <c r="C7" t="n">
-        <v>201.4585559022625</v>
+        <v>208.7647223172672</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>46.41212271826796</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.03871443328891</v>
+        <v>27.95526587842792</v>
       </c>
       <c r="C8" t="n">
-        <v>168.0653894900115</v>
+        <v>158.8025999004428</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>39.80496066868692</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>14.08906130364597</v>
       </c>
       <c r="C9" t="n">
-        <v>109.3843657117711</v>
+        <v>96.40467931392402</v>
       </c>
       <c r="D9" t="n">
-        <v>36.27655941962388</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>61.35432277690443</v>
+        <v>54.52135875534661</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.970121435402933</v>
+        <v>8.022310750403198</v>
       </c>
       <c r="C21" t="n">
-        <v>107.5966393779396</v>
+        <v>109.3039839742436</v>
       </c>
       <c r="D21" t="n">
-        <v>9.962651794253667</v>
+        <v>11.0306772818044</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.593417581721578</v>
+        <v>6.81136557206437</v>
       </c>
       <c r="C2" t="n">
-        <v>7.615416941842508</v>
+        <v>8.829838851995813</v>
       </c>
       <c r="D2" t="n">
-        <v>14.03899217072939</v>
+        <v>23.6532474384184</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.61670178918302</v>
+        <v>22.57037972063417</v>
       </c>
       <c r="C3" t="n">
-        <v>60.42166245786995</v>
+        <v>48.97448422635213</v>
       </c>
       <c r="D3" t="n">
-        <v>76.99847244407734</v>
+        <v>72.38425823411733</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.85803179797848</v>
+        <v>23.36854060418683</v>
       </c>
       <c r="C4" t="n">
-        <v>130.6902543893354</v>
+        <v>104.3990508696058</v>
       </c>
       <c r="D4" t="n">
-        <v>113.9200401053914</v>
+        <v>94.40584098807754</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.72241174607219</v>
+        <v>31.09685853201772</v>
       </c>
       <c r="C5" t="n">
-        <v>122.5957445678205</v>
+        <v>117.8588118948296</v>
       </c>
       <c r="D5" t="n">
-        <v>67.81422267084844</v>
+        <v>59.12575548826417</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.33087433852696</v>
+        <v>27.57238427377167</v>
       </c>
       <c r="C6" t="n">
-        <v>132.669457761097</v>
+        <v>137.4996564659913</v>
       </c>
       <c r="D6" t="n">
-        <v>31.67805317293184</v>
+        <v>30.5510068084565</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.56484908730718</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>118.1562814492164</v>
+        <v>111.6286409636793</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>27.96704685087888</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>80.6113039957056</v>
+        <v>71.01472018669303</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70353755551324</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>46.81562102471339</v>
+        <v>41.60155896745857</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
         <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.028110830524663</v>
+        <v>4.238204839233481</v>
       </c>
       <c r="C2" t="n">
-        <v>3.889684404225862</v>
+        <v>4.828235209485814</v>
       </c>
       <c r="D2" t="n">
-        <v>10.24650078922396</v>
+        <v>16.48550744971244</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.05005343738336</v>
+        <v>23.58648859452962</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9703362513569</v>
+        <v>42.46058820867455</v>
       </c>
       <c r="D3" t="n">
-        <v>71.81484456565418</v>
+        <v>75.14787802157211</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.86476516318797</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="C4" t="n">
-        <v>144.8951619220825</v>
+        <v>116.8044148604685</v>
       </c>
       <c r="D4" t="n">
-        <v>125.0618948008884</v>
+        <v>105.9433400083861</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.13398501832986</v>
+        <v>34.55751918948773</v>
       </c>
       <c r="C5" t="n">
-        <v>176.591868301395</v>
+        <v>153.3489914033518</v>
       </c>
       <c r="D5" t="n">
-        <v>84.47938995043805</v>
+        <v>73.72925258893547</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.12082138754715</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C6" t="n">
-        <v>161.8116566139593</v>
+        <v>165.1525440515112</v>
       </c>
       <c r="D6" t="n">
-        <v>39.08435785376978</v>
+        <v>37.43403996293088</v>
       </c>
     </row>
     <row r="7">
@@ -2097,10 +2097,10 @@
         <v>17.24734366820796</v>
       </c>
       <c r="C7" t="n">
-        <v>148.6984525283346</v>
+        <v>146.0035550801771</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>104.6444877956675</v>
+        <v>94.29686699290613</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>50.80937068558941</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
         <v>28.39999758845172</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.292781800043802</v>
+        <v>3.768929436603505</v>
       </c>
       <c r="C2" t="n">
-        <v>14.30013706005904</v>
+        <v>9.451285148784043</v>
       </c>
       <c r="D2" t="n">
-        <v>12.29933523880404</v>
+        <v>12.5271007061893</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.87762569433442</v>
+        <v>18.97227438456961</v>
       </c>
       <c r="C3" t="n">
-        <v>30.28200793749286</v>
+        <v>29.82058651649687</v>
       </c>
       <c r="D3" t="n">
-        <v>64.18666490365646</v>
+        <v>71.08344252599031</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.55693835241098</v>
+        <v>38.27539774547039</v>
       </c>
       <c r="C4" t="n">
-        <v>129.9372539001781</v>
+        <v>112.3502255263007</v>
       </c>
       <c r="D4" t="n">
-        <v>131.3156276769406</v>
+        <v>117.3149236666768</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.28816046562561</v>
+        <v>40.61981126321179</v>
       </c>
       <c r="C5" t="n">
-        <v>218.9542817396449</v>
+        <v>182.9977720716055</v>
       </c>
       <c r="D5" t="n">
-        <v>105.8569462104124</v>
+        <v>91.4497986505904</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.51454327467913</v>
+        <v>39.00385454202154</v>
       </c>
       <c r="C6" t="n">
-        <v>217.077180129125</v>
+        <v>201.6607959293374</v>
       </c>
       <c r="D6" t="n">
-        <v>52.89067581859268</v>
+        <v>48.94601354292898</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.27214940272139</v>
+        <v>25.930902112271</v>
       </c>
       <c r="C7" t="n">
-        <v>187.9241820515159</v>
+        <v>190.3196464498782</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C8" t="n">
-        <v>143.7818600254666</v>
+        <v>139.0252923983908</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>83.75780538781659</v>
+        <v>76.87968097186344</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.00374706436774</v>
+        <v>2.267837196810132</v>
       </c>
       <c r="C2" t="n">
-        <v>6.932120539686728</v>
+        <v>4.518002934943821</v>
       </c>
       <c r="D2" t="n">
-        <v>8.610909113948773</v>
+        <v>8.746390297134834</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95969159086365</v>
+        <v>18.28014225307561</v>
       </c>
       <c r="C3" t="n">
-        <v>42.64712027248144</v>
+        <v>34.68023765251858</v>
       </c>
       <c r="D3" t="n">
-        <v>62.46860642122455</v>
+        <v>68.60943831128834</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.09221183540375</v>
+        <v>42.168027392809</v>
       </c>
       <c r="C4" t="n">
-        <v>123.9770635876957</v>
+        <v>109.7593933347934</v>
       </c>
       <c r="D4" t="n">
-        <v>137.7480386351657</v>
+        <v>125.6617426481832</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.83441309981433</v>
+        <v>42.16606389740051</v>
       </c>
       <c r="C5" t="n">
-        <v>262.2248118043231</v>
+        <v>217.6780097241241</v>
       </c>
       <c r="D5" t="n">
-        <v>110.6429662686156</v>
+        <v>96.62851779049234</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.22899356146354</v>
+        <v>31.5975498611836</v>
       </c>
       <c r="C6" t="n">
-        <v>248.1112068080709</v>
+        <v>241.5099352447154</v>
       </c>
       <c r="D6" t="n">
-        <v>51.20010627187966</v>
+        <v>48.26173539306896</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>193.313976947831</v>
+        <v>192.4156777984451</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>102.558273924143</v>
+        <v>98.88653751025997</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
         <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.86866679180918</v>
+        <v>3.066979828067036</v>
       </c>
       <c r="C2" t="n">
-        <v>9.154797342101507</v>
+        <v>4.886158324036376</v>
       </c>
       <c r="D2" t="n">
-        <v>12.86285842104171</v>
+        <v>8.968265278294613</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.22766765639402</v>
+        <v>13.12596680577985</v>
       </c>
       <c r="C3" t="n">
-        <v>35.00421439492003</v>
+        <v>26.01140542401924</v>
       </c>
       <c r="D3" t="n">
-        <v>55.88107932572845</v>
+        <v>61.27087422204344</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.87600635629119</v>
+        <v>39.14326271602458</v>
       </c>
       <c r="C4" t="n">
-        <v>116.6767876589164</v>
+        <v>99.30672552767761</v>
       </c>
       <c r="D4" t="n">
-        <v>137.339631590199</v>
+        <v>129.9372539001781</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.5411325781518</v>
+        <v>51.05088062083415</v>
       </c>
       <c r="C5" t="n">
-        <v>246.7131980772235</v>
+        <v>212.3029410433728</v>
       </c>
       <c r="D5" t="n">
-        <v>130.5479009722196</v>
+        <v>114.5699570856028</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.04410619789565</v>
+        <v>41.37870223859457</v>
       </c>
       <c r="C6" t="n">
-        <v>324.1465847542822</v>
+        <v>289.3691540790432</v>
       </c>
       <c r="D6" t="n">
-        <v>66.77749709516381</v>
+        <v>62.43031826075894</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>260.5666399318502</v>
+        <v>261.5248256911951</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>161.7232993205771</v>
+        <v>160.4715709976624</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>65.23124446097505</v>
+        <v>63.6781195928566</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.938951715887451</v>
+        <v>2.092104357749953</v>
       </c>
       <c r="C2" t="n">
-        <v>4.873395603881167</v>
+        <v>3.769911184307752</v>
       </c>
       <c r="D2" t="n">
-        <v>9.220574438286043</v>
+        <v>8.00222553731575</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.28518986031709</v>
+        <v>12.10985793188441</v>
       </c>
       <c r="C3" t="n">
-        <v>35.87796985169969</v>
+        <v>23.33123419142545</v>
       </c>
       <c r="D3" t="n">
-        <v>53.87340527054372</v>
+        <v>56.55357650313752</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.03442758957343</v>
+        <v>34.43381897875263</v>
       </c>
       <c r="C4" t="n">
-        <v>106.8750185797163</v>
+        <v>86.67163257402116</v>
       </c>
       <c r="D4" t="n">
-        <v>135.4635117273834</v>
+        <v>130.8944579118187</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.82998738737862</v>
+        <v>55.61600744558182</v>
       </c>
       <c r="C5" t="n">
-        <v>243.5470617310275</v>
+        <v>208.4495813042041</v>
       </c>
       <c r="D5" t="n">
-        <v>143.1879026643973</v>
+        <v>126.4736479995954</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.00135126726531</v>
+        <v>48.46299367243955</v>
       </c>
       <c r="C6" t="n">
-        <v>360.4133266968636</v>
+        <v>319.1151277700173</v>
       </c>
       <c r="D6" t="n">
-        <v>78.61148392215486</v>
+        <v>74.34480839949822</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.43267300013236</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>326.0825912270568</v>
+        <v>319.0758578618473</v>
       </c>
       <c r="D7" t="n">
-        <v>43.35790561035613</v>
+        <v>42.87881273068369</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>204.8662021837031</v>
+        <v>206.8689675003666</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>69.33593161243097</v>
+        <v>72.66405632982764</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.06233313145306</v>
+      </c>
+      <c r="D14" t="n">
         <v>10.75504610002381</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4626241528785</v>
+        <v>3.2319134423805</v>
       </c>
       <c r="C2" t="n">
-        <v>7.71948219849267</v>
+        <v>6.94095626902495</v>
       </c>
       <c r="D2" t="n">
-        <v>17.3278469799562</v>
+        <v>12.05586180815083</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.076257525761761</v>
+        <v>9.714393533522189</v>
       </c>
       <c r="C3" t="n">
-        <v>28.50504459280614</v>
+        <v>19.39933463591697</v>
       </c>
       <c r="D3" t="n">
-        <v>49.63716392671873</v>
+        <v>50.94779711188823</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.0697294491973</v>
+        <v>29.03518835309942</v>
       </c>
       <c r="C4" t="n">
-        <v>99.29396280752239</v>
+        <v>74.12587866145118</v>
       </c>
       <c r="D4" t="n">
-        <v>131.953763684701</v>
+        <v>129.2353042916416</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.60280275707011</v>
+        <v>54.58517235612267</v>
       </c>
       <c r="C5" t="n">
-        <v>224.2311756499715</v>
+        <v>187.6610736667778</v>
       </c>
       <c r="D5" t="n">
-        <v>153.4717098663827</v>
+        <v>139.4572613882594</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.09193409796327</v>
+        <v>57.51961624411638</v>
       </c>
       <c r="C6" t="n">
-        <v>371.4422804063723</v>
+        <v>324.9918695276387</v>
       </c>
       <c r="D6" t="n">
-        <v>94.83290123942491</v>
+        <v>89.96245087865648</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.35010838198439</v>
+        <v>29.34443887993716</v>
       </c>
       <c r="C7" t="n">
-        <v>398.0064097878824</v>
+        <v>375.3692712233595</v>
       </c>
       <c r="D7" t="n">
-        <v>51.56237117474672</v>
+        <v>50.36463897556562</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.260024272905162</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>285.3940576245478</v>
+        <v>290.3175223613455</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>131.571863827749</v>
+        <v>136.0093634509446</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.26133448244146</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.527239574909543</v>
+        <v>4.334416114249668</v>
       </c>
       <c r="C2" t="n">
-        <v>11.66021748333937</v>
+        <v>5.782493978013713</v>
       </c>
       <c r="D2" t="n">
-        <v>5.431028299893355</v>
+        <v>5.995533229835271</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.554507526450201</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C2" t="n">
-        <v>4.630903920932204</v>
+        <v>3.998658399397259</v>
       </c>
       <c r="D2" t="n">
-        <v>12.89231085216911</v>
+        <v>8.969247025998859</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.38474728907351</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C3" t="n">
-        <v>33.89974822764236</v>
+        <v>24.53387512912779</v>
       </c>
       <c r="D3" t="n">
-        <v>56.39649687045802</v>
+        <v>55.62091618410305</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.66278717802039</v>
+        <v>41.03214529899544</v>
       </c>
       <c r="C4" t="n">
-        <v>137.5693605529928</v>
+        <v>106.9133067401819</v>
       </c>
       <c r="D4" t="n">
-        <v>136.4590038994896</v>
+        <v>132.7833404947896</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.89421759431538</v>
+        <v>33.40396563699773</v>
       </c>
       <c r="C5" t="n">
-        <v>324.1240045570845</v>
+        <v>278.0064061500906</v>
       </c>
       <c r="D5" t="n">
-        <v>137.9110087540707</v>
+        <v>127.283589855599</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.34217228489241</v>
+        <v>18.19374845510189</v>
       </c>
       <c r="C6" t="n">
-        <v>324.0258297866598</v>
+        <v>307.7641608135157</v>
       </c>
       <c r="D6" t="n">
-        <v>75.39135145222532</v>
+        <v>72.93600044390405</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.790928796724434</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>200.6800299727947</v>
+        <v>204.15345335042</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>32.03933632809466</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>96.96722074845746</v>
+        <v>100.2217143880356</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.0546844384641</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.9264920953685</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.395505456091222</v>
+        <v>6.240970155896973</v>
       </c>
       <c r="C2" t="n">
-        <v>4.841979677345269</v>
+        <v>8.294786353181301</v>
       </c>
       <c r="D2" t="n">
-        <v>24.39839394594173</v>
+        <v>16.00248757922301</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.74170254279185</v>
+        <v>9.213702204356315</v>
       </c>
       <c r="C3" t="n">
-        <v>29.38370878810703</v>
+        <v>14.79984664152067</v>
       </c>
       <c r="D3" t="n">
-        <v>7.696902001294993</v>
+        <v>8.413577825395164</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39811892905498</v>
+        <v>13.3992376361714</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14309321681725</v>
+        <v>70.14894997760324</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576249285771174</v>
+        <v>1.576380898373106</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.643666641087413</v>
+        <v>4.729078691356886</v>
       </c>
       <c r="C2" t="n">
-        <v>9.099819470663686</v>
+        <v>7.03618579633689</v>
       </c>
       <c r="D2" t="n">
-        <v>28.086820070797</v>
+        <v>20.68640587618454</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.98838325846506</v>
+        <v>16.57680998620739</v>
       </c>
       <c r="C3" t="n">
-        <v>22.81090790817464</v>
+        <v>26.10958019444392</v>
       </c>
       <c r="D3" t="n">
-        <v>26.33047342789946</v>
+        <v>19.82148614874311</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.69439872653876</v>
+        <v>10.83554941177205</v>
       </c>
       <c r="C4" t="n">
-        <v>45.32041927114551</v>
+        <v>23.08776076077224</v>
       </c>
       <c r="D4" t="n">
-        <v>19.10579207234717</v>
+        <v>19.47591095684822</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43809274759965</v>
+        <v>15.44363171370408</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12830690766121</v>
+        <v>86.15920850803327</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250124788968348</v>
+        <v>3.251290887095595</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.171445995344697</v>
+        <v>5.367214699117312</v>
       </c>
       <c r="C2" t="n">
-        <v>6.71613604475243</v>
+        <v>8.740499810909354</v>
       </c>
       <c r="D2" t="n">
-        <v>28.09467405243097</v>
+        <v>18.38126226661303</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.95616551067416</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C3" t="n">
-        <v>30.30655163009904</v>
+        <v>26.88025214227767</v>
       </c>
       <c r="D3" t="n">
-        <v>42.68639018065132</v>
+        <v>31.76935570942678</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.42708561354314</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="C4" t="n">
-        <v>52.16123727433728</v>
+        <v>47.97506506342888</v>
       </c>
       <c r="D4" t="n">
-        <v>27.98864530037232</v>
+        <v>25.02769422436394</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.07549676223577</v>
+        <v>10.03837027592364</v>
       </c>
       <c r="C5" t="n">
-        <v>49.21010367537139</v>
+        <v>26.60536278508857</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>29.45243112740432</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72490529259195</v>
+        <v>16.73861509477792</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0219222848109</v>
+        <v>102.1055520781454</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181226323147988</v>
+        <v>5.021584528433378</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.739297079026853</v>
+        <v>5.455571992499525</v>
       </c>
       <c r="C2" t="n">
-        <v>8.114144775599888</v>
+        <v>10.51059092166635</v>
       </c>
       <c r="D2" t="n">
-        <v>22.68818944514379</v>
+        <v>24.96388062358789</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.93376523992573</v>
+        <v>17.52419652080557</v>
       </c>
       <c r="C3" t="n">
-        <v>27.86690858504571</v>
+        <v>30.92996142229576</v>
       </c>
       <c r="D3" t="n">
-        <v>54.54099370943155</v>
+        <v>38.67104207028186</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.37076614150258</v>
+        <v>27.8099672181994</v>
       </c>
       <c r="C4" t="n">
-        <v>65.12816095202915</v>
+        <v>58.28734294883738</v>
       </c>
       <c r="D4" t="n">
-        <v>42.27012915405066</v>
+        <v>34.76564970278805</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.11448893296516</v>
+        <v>21.99114857512856</v>
       </c>
       <c r="C5" t="n">
-        <v>73.70470889632931</v>
+        <v>60.69655181505907</v>
       </c>
       <c r="D5" t="n">
-        <v>32.54493639578177</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.02895370950867</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>46.249152599363</v>
+        <v>28.01515248838698</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03992220099619</v>
+        <v>18.06596799077078</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6890162636418</v>
+        <v>117.8589340350284</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013307400332063</v>
+        <v>6.882273520293629</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.243915399009714</v>
+        <v>6.370560852857552</v>
       </c>
       <c r="C2" t="n">
-        <v>14.07629858349077</v>
+        <v>9.957866964175397</v>
       </c>
       <c r="D2" t="n">
-        <v>29.13925360974958</v>
+        <v>23.22029670084556</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.93867397844697</v>
+        <v>16.17920216598743</v>
       </c>
       <c r="C3" t="n">
-        <v>28.06325812589508</v>
+        <v>34.38571334124453</v>
       </c>
       <c r="D3" t="n">
-        <v>56.12651625179015</v>
+        <v>46.13723336107886</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.34752299177014</v>
+        <v>22.60277739487432</v>
       </c>
       <c r="C4" t="n">
-        <v>56.5133248472634</v>
+        <v>57.73854598216341</v>
       </c>
       <c r="D4" t="n">
-        <v>51.62520302781852</v>
+        <v>39.87073776487146</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.43293504203962</v>
+        <v>19.68404147014855</v>
       </c>
       <c r="C5" t="n">
-        <v>72.40389318820228</v>
+        <v>63.3963580017378</v>
       </c>
       <c r="D5" t="n">
-        <v>32.37313054753858</v>
+        <v>29.42788743479815</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.43776166510284</v>
+        <v>10.78744377426395</v>
       </c>
       <c r="C6" t="n">
-        <v>55.99005332089985</v>
+        <v>43.1095234411817</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>27.96704685087888</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.045960765671207</v>
+        <v>7.06052237960763</v>
       </c>
       <c r="C21" t="n">
-        <v>66.05588217816756</v>
+        <v>66.19239730882154</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403725478544505</v>
+        <v>5.295391784705723</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.46637121724624</v>
+        <v>5.517422097867075</v>
       </c>
       <c r="C2" t="n">
-        <v>10.57145927932965</v>
+        <v>5.571418221600648</v>
       </c>
       <c r="D2" t="n">
-        <v>24.55252833550848</v>
+        <v>20.82286880707485</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.63986282345744</v>
+        <v>19.98347451994383</v>
       </c>
       <c r="C3" t="n">
-        <v>45.14566817978957</v>
+        <v>37.30641276137879</v>
       </c>
       <c r="D3" t="n">
-        <v>67.03864198449345</v>
+        <v>54.49190632421922</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.5164246546296</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="C4" t="n">
-        <v>65.12816095202915</v>
+        <v>75.68293052038661</v>
       </c>
       <c r="D4" t="n">
-        <v>69.05907875983338</v>
+        <v>54.42023874180919</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.08427573831176</v>
+        <v>28.1516154192773</v>
       </c>
       <c r="C5" t="n">
-        <v>91.76886665447061</v>
+        <v>89.95263340161401</v>
       </c>
       <c r="D5" t="n">
-        <v>43.9086660724386</v>
+        <v>38.04272353956391</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.37992066601029</v>
+        <v>19.76356303419254</v>
       </c>
       <c r="C6" t="n">
-        <v>90.24421246977532</v>
+        <v>76.5989011284489</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>33.65038431076368</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.77958979262998</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>58.26967149016093</v>
+        <v>44.97484407925062</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>29.12354564648163</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.262059478878444</v>
+        <v>7.282158911331938</v>
       </c>
       <c r="C21" t="n">
-        <v>75.34386709336387</v>
+        <v>75.55239870506887</v>
       </c>
       <c r="D21" t="n">
-        <v>5.446544609158833</v>
+        <v>6.371889047415446</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.435536127787089</v>
+        <v>3.764020698082271</v>
       </c>
       <c r="C2" t="n">
-        <v>7.505461198966865</v>
+        <v>5.206208075620835</v>
       </c>
       <c r="D2" t="n">
-        <v>23.50893052589412</v>
+        <v>15.18272824617692</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3600647277471</v>
+        <v>19.49260066782042</v>
       </c>
       <c r="C3" t="n">
-        <v>42.73547756586365</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D3" t="n">
-        <v>70.78891821471626</v>
+        <v>58.50725443458867</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.10649608261094</v>
+        <v>34.52315801983909</v>
       </c>
       <c r="C4" t="n">
-        <v>92.36380576324416</v>
+        <v>85.24220791663781</v>
       </c>
       <c r="D4" t="n">
-        <v>85.48469959958678</v>
+        <v>69.5185366854209</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.78470381979624</v>
+        <v>35.93196597543326</v>
       </c>
       <c r="C5" t="n">
-        <v>106.6423443738098</v>
+        <v>118.49694790259</v>
       </c>
       <c r="D5" t="n">
-        <v>58.78214379177778</v>
+        <v>48.67014243803564</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.15478164656829</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C6" t="n">
-        <v>120.4329543753648</v>
+        <v>113.1474046621492</v>
       </c>
       <c r="D6" t="n">
-        <v>40.01014593887452</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>96.95642152371074</v>
+        <v>80.30794395509334</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>54.57535487908019</v>
+        <v>43.39324852770901</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>30.28593492830985</v>
+        <v>27.17968519207294</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.463471043871384</v>
+        <v>7.490207525304696</v>
       </c>
       <c r="C21" t="n">
-        <v>83.96404924355308</v>
+        <v>84.26483465967783</v>
       </c>
       <c r="D21" t="n">
-        <v>6.530537163387462</v>
+        <v>7.490207525304696</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_34_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634344255</v>
+        <v>10.8449764980426</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907198103142</v>
+        <v>37.78907251973175</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.750096303773569</v>
+        <v>1.592394776288327</v>
       </c>
       <c r="C2" t="n">
-        <v>9.503317777109125</v>
+        <v>2.621266370338984</v>
       </c>
       <c r="D2" t="n">
-        <v>29.11176467403067</v>
+        <v>14.47783339452771</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90922154731956</v>
+        <v>11.58462291011236</v>
       </c>
       <c r="C3" t="n">
-        <v>23.68957210347553</v>
+        <v>33.23706852727577</v>
       </c>
       <c r="D3" t="n">
-        <v>56.98554549300611</v>
+        <v>72.02101158354601</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.90153179660161</v>
+        <v>15.96616291416588</v>
       </c>
       <c r="C4" t="n">
-        <v>77.26550781963248</v>
+        <v>88.96892220195869</v>
       </c>
       <c r="D4" t="n">
-        <v>81.00498482510856</v>
+        <v>94.3420273873015</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.12955930589413</v>
+        <v>16.51790512395259</v>
       </c>
       <c r="C5" t="n">
-        <v>137.5673970575843</v>
+        <v>73.23837873681207</v>
       </c>
       <c r="D5" t="n">
-        <v>61.87464906015524</v>
+        <v>57.13771638716437</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.1246095096439</v>
+        <v>11.7132318593687</v>
       </c>
       <c r="C6" t="n">
-        <v>151.6682393336813</v>
+        <v>39.7686360036298</v>
       </c>
       <c r="D6" t="n">
-        <v>44.23656980565704</v>
+        <v>31.67805317293184</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.35010838198439</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>122.5280039762274</v>
+        <v>27.90716024091983</v>
       </c>
       <c r="D7" t="n">
-        <v>38.74663664350886</v>
+        <v>29.64387192973244</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>74.43611093599316</v>
+        <v>27.78836876870596</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.02701557629594</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.47216389248049</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.683800288756356</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.16607850117082</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.6442753248509</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.575746123045136</v>
+        <v>1.661117115585603</v>
       </c>
       <c r="C2" t="n">
-        <v>8.803331663981149</v>
+        <v>6.346017160251383</v>
       </c>
       <c r="D2" t="n">
-        <v>22.58706943160637</v>
+        <v>18.4666743168825</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.42602175038088</v>
+        <v>8.251589454194441</v>
       </c>
       <c r="C3" t="n">
-        <v>30.22310307523806</v>
+        <v>19.26679869584365</v>
       </c>
       <c r="D3" t="n">
-        <v>65.19786503903067</v>
+        <v>66.89137982885642</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.80019079888594</v>
+        <v>19.79497896072844</v>
       </c>
       <c r="C4" t="n">
-        <v>67.54031506136356</v>
+        <v>86.51847993215866</v>
       </c>
       <c r="D4" t="n">
-        <v>89.49219372832225</v>
+        <v>109.3126981293611</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.79286090106649</v>
+        <v>20.76396394482004</v>
       </c>
       <c r="C5" t="n">
-        <v>139.7763293921396</v>
+        <v>125.0010264432252</v>
       </c>
       <c r="D5" t="n">
-        <v>73.80288366675398</v>
+        <v>78.04894248762143</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.18123208132072</v>
+        <v>16.9459471230042</v>
       </c>
       <c r="C6" t="n">
-        <v>181.3739613687813</v>
+        <v>80.5838150599867</v>
       </c>
       <c r="D6" t="n">
-        <v>52.40765594810324</v>
+        <v>42.2642386678252</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.45287309576081</v>
+        <v>9.941177253203202</v>
       </c>
       <c r="C7" t="n">
-        <v>167.9220543251914</v>
+        <v>43.47767883027424</v>
       </c>
       <c r="D7" t="n">
-        <v>41.9206269713388</v>
+        <v>32.03933632809466</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.27799883121787</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>114.2410716046801</v>
+        <v>33.12907627980861</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>64.6765570080756</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.91549724863931</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.83695743229957</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.860897053161644</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2090495594562</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.826121316452054</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.448519832120549</v>
+        <v>0.8551022503989718</v>
       </c>
       <c r="C2" t="n">
-        <v>12.83438773761855</v>
+        <v>2.552544031041707</v>
       </c>
       <c r="D2" t="n">
-        <v>28.76618948213579</v>
+        <v>12.50452050899162</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.08517537055799</v>
+        <v>7.942338927356696</v>
       </c>
       <c r="C3" t="n">
-        <v>31.80371687907542</v>
+        <v>23.23305942100077</v>
       </c>
       <c r="D3" t="n">
-        <v>66.74902641174064</v>
+        <v>68.32473147705677</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.16205479112551</v>
+        <v>22.09226858866597</v>
       </c>
       <c r="C4" t="n">
-        <v>70.89691046218341</v>
+        <v>78.8097969584127</v>
       </c>
       <c r="D4" t="n">
-        <v>97.43060566486196</v>
+        <v>118.667772003129</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.64559874542947</v>
+        <v>21.25483779694345</v>
       </c>
       <c r="C5" t="n">
-        <v>131.4314739060418</v>
+        <v>152.3181563138926</v>
       </c>
       <c r="D5" t="n">
-        <v>85.70657458074656</v>
+        <v>89.04451677518571</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.2252718592916</v>
+        <v>13.92707293244525</v>
       </c>
       <c r="C6" t="n">
-        <v>197.2733654390584</v>
+        <v>111.9801066417997</v>
       </c>
       <c r="D6" t="n">
-        <v>60.41773546705297</v>
+        <v>42.74725853831463</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.43586458961913</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>208.7647223172672</v>
+        <v>45.93302983859552</v>
       </c>
       <c r="D7" t="n">
-        <v>46.41212271826796</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.95526587842792</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>158.8025999004428</v>
+        <v>38.05254101660637</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>96.40467931392402</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>54.52135875534661</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.022310750403198</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3039839742436</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0306772818044</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.81136557206437</v>
+        <v>0.7294385442553801</v>
       </c>
       <c r="C2" t="n">
-        <v>8.829838851995813</v>
+        <v>6.049529353568845</v>
       </c>
       <c r="D2" t="n">
-        <v>23.6532474384184</v>
+        <v>11.54437125423824</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.57037972063417</v>
+        <v>5.325981295538947</v>
       </c>
       <c r="C3" t="n">
-        <v>48.97448422635213</v>
+        <v>15.5116137270996</v>
       </c>
       <c r="D3" t="n">
-        <v>72.38425823411733</v>
+        <v>62.63059479242527</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.36854060418683</v>
+        <v>18.82501222893259</v>
       </c>
       <c r="C4" t="n">
-        <v>104.3990508696058</v>
+        <v>67.84662034508857</v>
       </c>
       <c r="D4" t="n">
-        <v>94.40584098807754</v>
+        <v>125.8148952900457</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.09685853201772</v>
+        <v>27.56256679672921</v>
       </c>
       <c r="C5" t="n">
-        <v>117.8588118948296</v>
+        <v>151.6800203061322</v>
       </c>
       <c r="D5" t="n">
-        <v>59.12575548826417</v>
+        <v>111.2320148911636</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.57238427377167</v>
+        <v>20.64909946342317</v>
       </c>
       <c r="C6" t="n">
-        <v>137.4996564659913</v>
+        <v>178.0330739312294</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5510068084565</v>
+        <v>58.00263611460582</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>111.6286409636793</v>
+        <v>102.3462164200257</v>
       </c>
       <c r="D7" t="n">
-        <v>27.96704685087888</v>
+        <v>38.32743037379547</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>71.01472018669303</v>
+        <v>50.06913291658733</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
+        <v>36.49843440078366</v>
+      </c>
+      <c r="D9" t="n">
         <v>41.60155896745857</v>
-      </c>
-      <c r="D9" t="n">
-        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.98534020436108</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.238204839233481</v>
+        <v>0.4643666641087413</v>
       </c>
       <c r="C2" t="n">
-        <v>4.828235209485814</v>
+        <v>3.764020698082271</v>
       </c>
       <c r="D2" t="n">
-        <v>16.48550744971244</v>
+        <v>8.40277860064845</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.58648859452962</v>
+        <v>4.084070449666732</v>
       </c>
       <c r="C3" t="n">
-        <v>42.46058820867455</v>
+        <v>20.2681813541754</v>
       </c>
       <c r="D3" t="n">
-        <v>75.14787802157211</v>
+        <v>58.8165049614264</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.91956310817654</v>
+        <v>15.74919667152733</v>
       </c>
       <c r="C4" t="n">
-        <v>116.8044148604685</v>
+        <v>55.1732392309665</v>
       </c>
       <c r="D4" t="n">
-        <v>105.9433400083861</v>
+        <v>128.8779481272958</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.55751918948773</v>
+        <v>29.550605897829</v>
       </c>
       <c r="C5" t="n">
-        <v>153.3489914033518</v>
+        <v>145.1759417654971</v>
       </c>
       <c r="D5" t="n">
-        <v>73.72925258893547</v>
+        <v>127.5535704742669</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.96610616090365</v>
+        <v>26.00256969468102</v>
       </c>
       <c r="C6" t="n">
-        <v>165.1525440515112</v>
+        <v>211.7639615537413</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>71.52719248830986</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>146.0035550801771</v>
+        <v>161.2746406197363</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>94.29686699290613</v>
+        <v>74.35266238113219</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>46.70468353413349</v>
+        <v>46.59374604355361</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.768929436603505</v>
+        <v>1.164352777236717</v>
       </c>
       <c r="C2" t="n">
-        <v>9.451285148784043</v>
+        <v>6.570837384523903</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5271007061893</v>
+        <v>15.44583663091507</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.97227438456961</v>
+        <v>2.812707172667112</v>
       </c>
       <c r="C3" t="n">
-        <v>29.82058651649687</v>
+        <v>17.31802950291373</v>
       </c>
       <c r="D3" t="n">
-        <v>71.08344252599031</v>
+        <v>52.34678759043993</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.27539774547039</v>
+        <v>11.84380430403352</v>
       </c>
       <c r="C4" t="n">
-        <v>112.3502255263007</v>
+        <v>52.7866105619425</v>
       </c>
       <c r="D4" t="n">
-        <v>117.3149236666768</v>
+        <v>129.1076770900895</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.61981126321179</v>
+        <v>27.51347941151687</v>
       </c>
       <c r="C5" t="n">
-        <v>182.9977720716055</v>
+        <v>124.7801332097696</v>
       </c>
       <c r="D5" t="n">
-        <v>91.4497986505904</v>
+        <v>143.286077434822</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.00385454202154</v>
+        <v>32.40258297866598</v>
       </c>
       <c r="C6" t="n">
-        <v>201.6607959293374</v>
+        <v>221.5451139311523</v>
       </c>
       <c r="D6" t="n">
-        <v>48.94601354292898</v>
+        <v>91.69327208124361</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.930902112271</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>190.3196464498782</v>
+        <v>230.5634483423634</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>52.22112388429633</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>139.0252923983908</v>
+        <v>136.9390785268664</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>42.72566008882119</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>76.87968097186344</v>
+        <v>66.89530681967339</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>43.26562132615692</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.93999988351647</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.267837196810132</v>
+        <v>0.7726354432422398</v>
       </c>
       <c r="C2" t="n">
-        <v>4.518002934943821</v>
+        <v>3.363467634749572</v>
       </c>
       <c r="D2" t="n">
-        <v>8.746390297134834</v>
+        <v>11.12025624600362</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.28014225307561</v>
+        <v>4.388412237983242</v>
       </c>
       <c r="C3" t="n">
-        <v>34.68023765251858</v>
+        <v>23.09070600388498</v>
       </c>
       <c r="D3" t="n">
-        <v>68.60943831128834</v>
+        <v>57.8347572571796</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.168027392809</v>
+        <v>18.9909275909503</v>
       </c>
       <c r="C4" t="n">
-        <v>109.7593933347934</v>
+        <v>74.0237769002095</v>
       </c>
       <c r="D4" t="n">
-        <v>125.6617426481832</v>
+        <v>136.0250714142126</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.16606389740051</v>
+        <v>20.54307071136451</v>
       </c>
       <c r="C5" t="n">
-        <v>217.6780097241241</v>
+        <v>186.4829764216817</v>
       </c>
       <c r="D5" t="n">
-        <v>96.62851779049234</v>
+        <v>133.5913188553847</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.5975498611836</v>
+        <v>11.7132318593687</v>
       </c>
       <c r="C6" t="n">
-        <v>241.5099352447154</v>
+        <v>210.4759085657695</v>
       </c>
       <c r="D6" t="n">
-        <v>48.26173539306896</v>
+        <v>75.95487463446298</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>192.4156777984451</v>
+        <v>96.29766881416113</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>98.88653751025997</v>
+        <v>49.23464736797754</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.066979828067036</v>
+        <v>0.4123340357836604</v>
       </c>
       <c r="C2" t="n">
-        <v>4.886158324036376</v>
+        <v>2.991385254840031</v>
       </c>
       <c r="D2" t="n">
-        <v>8.968265278294613</v>
+        <v>7.994371555681777</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.12596680577985</v>
+        <v>3.495021827118645</v>
       </c>
       <c r="C3" t="n">
-        <v>26.01140542401924</v>
+        <v>17.5438314748905</v>
       </c>
       <c r="D3" t="n">
-        <v>61.27087422204344</v>
+        <v>53.36289646433539</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.14326271602458</v>
+        <v>12.8648219164502</v>
       </c>
       <c r="C4" t="n">
-        <v>99.30672552767761</v>
+        <v>63.36690557061038</v>
       </c>
       <c r="D4" t="n">
-        <v>129.9372539001781</v>
+        <v>128.9034735676062</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.05088062083415</v>
+        <v>19.5613230071177</v>
       </c>
       <c r="C5" t="n">
-        <v>212.3029410433728</v>
+        <v>145.298660228528</v>
       </c>
       <c r="D5" t="n">
-        <v>114.5699570856028</v>
+        <v>135.6529890343031</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.37870223859457</v>
+        <v>11.95474179461341</v>
       </c>
       <c r="C6" t="n">
-        <v>289.3691540790432</v>
+        <v>209.3488622012941</v>
       </c>
       <c r="D6" t="n">
-        <v>62.43031826075894</v>
+        <v>81.99262301558088</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>261.5248256911951</v>
+        <v>136.5414707066464</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>38.0279973240002</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>160.4715709976624</v>
+        <v>55.07604620824605</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>63.6781195928566</v>
+        <v>29.06562253193106</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.092104357749953</v>
+        <v>0.5458517235612266</v>
       </c>
       <c r="C2" t="n">
-        <v>3.769911184307752</v>
+        <v>9.05858606708532</v>
       </c>
       <c r="D2" t="n">
-        <v>8.00222553731575</v>
+        <v>17.12462520517711</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.10985793188441</v>
+        <v>2.32674205906494</v>
       </c>
       <c r="C3" t="n">
-        <v>23.33123419142545</v>
+        <v>14.08317081742049</v>
       </c>
       <c r="D3" t="n">
-        <v>56.55357650313752</v>
+        <v>47.37423546842984</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.43381897875263</v>
+        <v>9.712430038113695</v>
       </c>
       <c r="C4" t="n">
-        <v>86.67163257402116</v>
+        <v>51.98255919216436</v>
       </c>
       <c r="D4" t="n">
-        <v>130.8944579118187</v>
+        <v>126.8614383427728</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.61600744558182</v>
+        <v>19.9785657814226</v>
       </c>
       <c r="C5" t="n">
-        <v>208.4495813042041</v>
+        <v>130.8424252834937</v>
       </c>
       <c r="D5" t="n">
-        <v>126.4736479995954</v>
+        <v>151.9990883100124</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.46299367243955</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="C6" t="n">
-        <v>319.1151277700173</v>
+        <v>221.9878821457676</v>
       </c>
       <c r="D6" t="n">
-        <v>74.34480839949822</v>
+        <v>105.0970734873253</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>319.0758578618473</v>
+        <v>226.910365134861</v>
       </c>
       <c r="D7" t="n">
-        <v>42.87881273068369</v>
+        <v>51.62225778470578</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>206.8689675003666</v>
+        <v>120.4997132192535</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>72.66405632982764</v>
+        <v>49.14530832689106</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>17.94732978133594</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.2319134423805</v>
+        <v>0.6371542600561799</v>
       </c>
       <c r="C2" t="n">
-        <v>6.94095626902495</v>
+        <v>10.24355554611122</v>
       </c>
       <c r="D2" t="n">
-        <v>12.05586180815083</v>
+        <v>20.52343575727957</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.714393533522189</v>
+        <v>2.07148765596077</v>
       </c>
       <c r="C3" t="n">
-        <v>19.39933463591697</v>
+        <v>26.14394136409256</v>
       </c>
       <c r="D3" t="n">
-        <v>50.94779711188823</v>
+        <v>49.62243771115503</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.03518835309942</v>
+        <v>7.032258805519903</v>
       </c>
       <c r="C4" t="n">
-        <v>74.12587866145118</v>
+        <v>42.43604451606838</v>
       </c>
       <c r="D4" t="n">
-        <v>129.2353042916416</v>
+        <v>121.1437397132394</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.58517235612267</v>
+        <v>17.54874021341174</v>
       </c>
       <c r="C5" t="n">
-        <v>187.6610736667778</v>
+        <v>112.4101121362598</v>
       </c>
       <c r="D5" t="n">
-        <v>139.4572613882594</v>
+        <v>163.2646432162446</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.51961624411638</v>
+        <v>23.42646371873739</v>
       </c>
       <c r="C6" t="n">
-        <v>324.9918695276387</v>
+        <v>215.9903854205238</v>
       </c>
       <c r="D6" t="n">
-        <v>89.96245087865648</v>
+        <v>127.1952325622168</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.34443887993716</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>375.3692712233595</v>
+        <v>276.4365915709999</v>
       </c>
       <c r="D7" t="n">
-        <v>50.36463897556562</v>
+        <v>67.01311654418302</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>290.3175223613455</v>
+        <v>210.5407039142497</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>136.0093634509446</v>
+        <v>98.06874167262235</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.334416114249668</v>
+        <v>4.051672775426586</v>
       </c>
       <c r="C2" t="n">
-        <v>5.782493978013713</v>
+        <v>3.837651775900782</v>
       </c>
       <c r="D2" t="n">
-        <v>5.995533229835271</v>
+        <v>15.73937919448486</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.336559536107409</v>
+        <v>0.7215845626214056</v>
       </c>
       <c r="C2" t="n">
-        <v>3.998658399397259</v>
+        <v>7.572220042855649</v>
       </c>
       <c r="D2" t="n">
-        <v>8.969247025998859</v>
+        <v>21.03983504971339</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.18487166803466</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C3" t="n">
-        <v>24.53387512912779</v>
+        <v>32.87382187670445</v>
       </c>
       <c r="D3" t="n">
-        <v>55.62091618410305</v>
+        <v>53.49052366588747</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.03214529899544</v>
+        <v>5.475206946584461</v>
       </c>
       <c r="C4" t="n">
-        <v>106.9133067401819</v>
+        <v>53.15672944644354</v>
       </c>
       <c r="D4" t="n">
-        <v>132.7833404947896</v>
+        <v>118.7443483240602</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.40396563699773</v>
+        <v>14.65258448588365</v>
       </c>
       <c r="C5" t="n">
-        <v>278.0064061500906</v>
+        <v>95.86766331970105</v>
       </c>
       <c r="D5" t="n">
-        <v>127.283589855599</v>
+        <v>167.4370709592935</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.19374845510189</v>
+        <v>23.70822530985623</v>
       </c>
       <c r="C6" t="n">
-        <v>307.7641608135157</v>
+        <v>199.9299747267502</v>
       </c>
       <c r="D6" t="n">
-        <v>72.93600044390405</v>
+        <v>147.0795505640317</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>204.15345335042</v>
+        <v>292.9652959196991</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>84.260460212391</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>100.2217143880356</v>
+        <v>283.9754321919111</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>171.0656104741897</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>73.73907006597793</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.91890015564179</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.240970155896973</v>
+        <v>4.70944373727195</v>
       </c>
       <c r="C2" t="n">
-        <v>8.294786353181301</v>
+        <v>4.41982816451914</v>
       </c>
       <c r="D2" t="n">
-        <v>16.00248757922301</v>
+        <v>29.34542062764141</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.213702204356315</v>
+        <v>6.695519342963246</v>
       </c>
       <c r="C3" t="n">
-        <v>14.79984664152067</v>
+        <v>7.574183538264141</v>
       </c>
       <c r="D3" t="n">
-        <v>8.413577825395164</v>
+        <v>13.72974164389164</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3992376361714</v>
+        <v>11.67801612086504</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14894997760324</v>
+        <v>59.94714942044053</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576380898373106</v>
+        <v>0.7785344080576693</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.729078691356886</v>
+        <v>2.66249977391735</v>
       </c>
       <c r="C2" t="n">
-        <v>7.03618579633689</v>
+        <v>3.022801181375929</v>
       </c>
       <c r="D2" t="n">
-        <v>20.68640587618454</v>
+        <v>23.2399316549305</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.57680998620739</v>
+        <v>12.79217258633594</v>
       </c>
       <c r="C3" t="n">
-        <v>26.10958019444392</v>
+        <v>14.03408343220816</v>
       </c>
       <c r="D3" t="n">
-        <v>19.82148614874311</v>
+        <v>36.10377182367645</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.83554941177205</v>
+        <v>8.372344421816798</v>
       </c>
       <c r="C4" t="n">
-        <v>23.08776076077224</v>
+        <v>12.89034735676062</v>
       </c>
       <c r="D4" t="n">
-        <v>19.47591095684822</v>
+        <v>21.5307089018368</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44363171370408</v>
+        <v>13.62887132543755</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15920850803327</v>
+        <v>73.75624482001498</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251290887095595</v>
+        <v>1.603396626522065</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.367214699117312</v>
+        <v>1.598285262513807</v>
       </c>
       <c r="C2" t="n">
-        <v>8.740499810909354</v>
+        <v>3.50287580875262</v>
       </c>
       <c r="D2" t="n">
-        <v>18.38126226661303</v>
+        <v>25.51169584255761</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.46881773874025</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C3" t="n">
-        <v>26.88025214227767</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="D3" t="n">
-        <v>31.76935570942678</v>
+        <v>46.89808783187013</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.78145547704723</v>
+        <v>18.30174070256904</v>
       </c>
       <c r="C4" t="n">
-        <v>47.97506506342888</v>
+        <v>26.89105136702439</v>
       </c>
       <c r="D4" t="n">
-        <v>25.02769422436394</v>
+        <v>35.25063306868597</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.03837027592364</v>
+        <v>8.001243789611506</v>
       </c>
       <c r="C5" t="n">
-        <v>26.60536278508857</v>
+        <v>16.49336143134642</v>
       </c>
       <c r="D5" t="n">
-        <v>29.45243112740432</v>
+        <v>28.07798434145878</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>24.03318379996192</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73861509477792</v>
+        <v>14.84203711317044</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1055520781454</v>
+        <v>87.40310744422591</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021584528433378</v>
+        <v>2.473672852195073</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.455571992499525</v>
+        <v>1.554106615822701</v>
       </c>
       <c r="C2" t="n">
-        <v>10.51059092166635</v>
+        <v>9.620145753914496</v>
       </c>
       <c r="D2" t="n">
-        <v>24.96388062358789</v>
+        <v>20.04237938219863</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.52419652080557</v>
+        <v>7.780350556155972</v>
       </c>
       <c r="C3" t="n">
-        <v>30.92996142229576</v>
+        <v>13.24377653028947</v>
       </c>
       <c r="D3" t="n">
-        <v>38.67104207028186</v>
+        <v>56.42594930158543</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.8099672181994</v>
+        <v>20.02470792352219</v>
       </c>
       <c r="C4" t="n">
-        <v>58.28734294883738</v>
+        <v>29.71161252132547</v>
       </c>
       <c r="D4" t="n">
-        <v>34.76564970278805</v>
+        <v>50.47655821384976</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.99114857512856</v>
+        <v>18.30959468420302</v>
       </c>
       <c r="C5" t="n">
-        <v>60.69655181505907</v>
+        <v>35.76016012719008</v>
       </c>
       <c r="D5" t="n">
-        <v>31.48955761371645</v>
+        <v>34.82749980815561</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.861655689159212</v>
+        <v>7.929576207201488</v>
       </c>
       <c r="C6" t="n">
-        <v>28.01515248838698</v>
+        <v>19.24029150782899</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06596799077078</v>
+        <v>16.09112575660442</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8589340350284</v>
+        <v>101.6281626732911</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882273520293629</v>
+        <v>3.387605422443036</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.370560852857552</v>
+        <v>2.312015843501238</v>
       </c>
       <c r="C2" t="n">
-        <v>9.957866964175397</v>
+        <v>7.181484456565418</v>
       </c>
       <c r="D2" t="n">
-        <v>23.22029670084556</v>
+        <v>22.34359600095316</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.17920216598743</v>
+        <v>6.430447462816608</v>
       </c>
       <c r="C3" t="n">
-        <v>34.38571334124453</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D3" t="n">
-        <v>46.13723336107886</v>
+        <v>59.36628367580462</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.60277739487432</v>
+        <v>17.48492661263569</v>
       </c>
       <c r="C4" t="n">
-        <v>57.73854598216341</v>
+        <v>31.71535958569321</v>
       </c>
       <c r="D4" t="n">
-        <v>39.87073776487146</v>
+        <v>67.41268785981148</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.68404147014855</v>
+        <v>24.39643045053324</v>
       </c>
       <c r="C5" t="n">
-        <v>63.3963580017378</v>
+        <v>46.48575379608648</v>
       </c>
       <c r="D5" t="n">
-        <v>29.42788743479815</v>
+        <v>45.11130701014094</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.78744377426395</v>
+        <v>16.62393387601124</v>
       </c>
       <c r="C6" t="n">
-        <v>43.1095234411817</v>
+        <v>39.44662275663685</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>37.23278168356029</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>19.82246789644735</v>
+        <v>23.17611805415445</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.06052237960763</v>
+        <v>17.37191707170064</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19239730882154</v>
+        <v>115.5232485268093</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295391784705723</v>
+        <v>4.342979267925161</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.517422097867075</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C2" t="n">
-        <v>5.571418221600648</v>
+        <v>10.40947090812893</v>
       </c>
       <c r="D2" t="n">
-        <v>20.82286880707485</v>
+        <v>26.43257518914112</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.98347451994383</v>
+        <v>7.210936887692822</v>
       </c>
       <c r="C3" t="n">
-        <v>37.30641276137879</v>
+        <v>27.74419012201486</v>
       </c>
       <c r="D3" t="n">
-        <v>54.49190632421922</v>
+        <v>63.14110359863361</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.42257778564941</v>
+        <v>14.89409442112836</v>
       </c>
       <c r="C4" t="n">
-        <v>75.68293052038661</v>
+        <v>52.26333903557895</v>
       </c>
       <c r="D4" t="n">
-        <v>54.42023874180919</v>
+        <v>81.20918834759192</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.1516154192773</v>
+        <v>25.6727024660541</v>
       </c>
       <c r="C5" t="n">
-        <v>89.95263340161401</v>
+        <v>52.89165756629692</v>
       </c>
       <c r="D5" t="n">
-        <v>38.04272353956391</v>
+        <v>58.34035732486672</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.76356303419254</v>
+        <v>24.55351008321273</v>
       </c>
       <c r="C6" t="n">
-        <v>76.5989011284489</v>
+        <v>57.03659637362695</v>
       </c>
       <c r="D6" t="n">
-        <v>33.65038431076368</v>
+        <v>42.34474197957343</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>13.89369351050086</v>
       </c>
       <c r="C7" t="n">
-        <v>44.97484407925062</v>
+        <v>39.94436884268997</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>23.53249247079604</v>
+        <v>28.45595720759379</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.34594471145593</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.65056423721292</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.282158911331938</v>
+        <v>18.67790305451425</v>
       </c>
       <c r="C21" t="n">
-        <v>75.55239870506887</v>
+        <v>128.966473471646</v>
       </c>
       <c r="D21" t="n">
-        <v>6.371889047415446</v>
+        <v>5.336543729861215</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.764020698082271</v>
+        <v>3.479313863850696</v>
       </c>
       <c r="C2" t="n">
-        <v>5.206208075620835</v>
+        <v>6.244897146713961</v>
       </c>
       <c r="D2" t="n">
-        <v>15.18272824617692</v>
+        <v>20.63240975245097</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.49260066782042</v>
+        <v>9.979465413668827</v>
       </c>
       <c r="C3" t="n">
-        <v>28.18597658892593</v>
+        <v>43.40797474327272</v>
       </c>
       <c r="D3" t="n">
-        <v>58.50725443458867</v>
+        <v>71.57431637811372</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.52315801983909</v>
+        <v>12.32878766993144</v>
       </c>
       <c r="C4" t="n">
-        <v>85.24220791663781</v>
+        <v>60.01031016979053</v>
       </c>
       <c r="D4" t="n">
-        <v>69.5185366854209</v>
+        <v>76.21896476690537</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.93196597543326</v>
+        <v>13.81809893727386</v>
       </c>
       <c r="C5" t="n">
-        <v>118.49694790259</v>
+        <v>34.06664533736433</v>
       </c>
       <c r="D5" t="n">
-        <v>48.67014243803564</v>
+        <v>42.65693774952392</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.82647700272235</v>
+        <v>8.613854357061516</v>
       </c>
       <c r="C6" t="n">
-        <v>113.1474046621492</v>
+        <v>26.28433128579986</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>26.20382797405162</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>80.30794395509334</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>43.39324852770901</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.17968519207294</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.490207525304696</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.26483465967783</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.490207525304696</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
